--- a/docs/qa/upload-templates/routing_upload_template.xlsx
+++ b/docs/qa/upload-templates/routing_upload_template.xlsx
@@ -133,12 +133,17 @@
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Integer sequence</t>
+        <t>Integer sequence 10/20/30…</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Must exist</t>
+        <t>Must exist in work centre master</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Run time minutes</t>
       </text>
     </comment>
   </commentList>
@@ -434,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,6 +463,21 @@
           <t>run_minutes</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>setup_minutes</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>overlap_pct</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -476,6 +496,17 @@
       <c r="D2" t="n">
         <v>240</v>
       </c>
+      <c r="E2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>LV/HV winding</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -494,6 +525,17 @@
       <c r="D3" t="n">
         <v>120</v>
       </c>
+      <c r="E3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tank assembly</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -511,6 +553,17 @@
       </c>
       <c r="D4" t="n">
         <v>360</v>
+      </c>
+      <c r="E4" t="n">
+        <v>40</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>LV/HV winding</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
